--- a/outputs/march.xlsx
+++ b/outputs/march.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,6 +468,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -501,6 +546,37 @@
           <t>03/02/26</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>68058.35000000001</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>-1411.56</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>68891.21000000001</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>69453.88</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>66445.78999999999</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>178027060</v>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,12 +602,39 @@
       <c r="G3" s="1" t="n">
         <v>97.77</v>
       </c>
-      <c r="H3" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H3" s="3" t="n"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
           <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>99.06</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>98.43000000000001</v>
+      </c>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>17:38 ET</t>
         </is>
       </c>
     </row>
@@ -567,6 +670,37 @@
           <t>03/02/26</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>0.86937</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>-0.00255</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>0.87192</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>0.8739400000000001</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>0.86913</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>721523</v>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -600,6 +734,37 @@
           <t>03/02/26</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0.5501</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0.5528999999999999</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>0.5554</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>0.5456</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>1227126</v>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -633,6 +798,37 @@
           <t>03/02/26</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>1.36789</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0.00032</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>1.36757</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>1.3753</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>1.36533</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>510310</v>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -666,6 +862,37 @@
           <t>03/02/26</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.96241</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>-0.00783</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.97023</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.97309</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0.9546</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>522134</v>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -699,6 +926,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -732,6 +990,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -765,6 +1054,37 @@
           <t>03/02/26</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>82.053</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>-7.298</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>-8.17</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>89.34999999999999</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>91.322</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>78.09099999999999</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>208906</v>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -798,6 +1118,37 @@
           <t>03/02/26</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>5088.38</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>-233.64</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>5322.02</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>5379.89</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>4997.76</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>201061</v>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -831,6 +1182,37 @@
           <t>03/02/26</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0.5716</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0.5699</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.5744</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.5693</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>375683</v>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -864,6 +1246,37 @@
           <t>03/02/26</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>1.58846</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>-0.01038</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>1.59882</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>1.59956</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>1.58374</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>523927</v>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -897,6 +1310,37 @@
           <t>03/02/26</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>157.728</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>157.358</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>157.968</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>157.151</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>708637</v>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -930,6 +1374,37 @@
           <t>03/02/26</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>0.90801</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>-0.00307</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>0.91107</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>0.91278</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>0.9067</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>592234</v>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -961,6 +1436,37 @@
       <c r="I16" s="4" t="inlineStr">
         <is>
           <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>0.7819199999999999</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0.00251</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>0.77941</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>0.78787</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>0.7784799999999999</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>541402</v>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
         </is>
       </c>
     </row>

--- a/outputs/march.xlsx
+++ b/outputs/march.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,6 +420,2592 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:BA16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>69469.91</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>3938.81</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>65712.14</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>69995.41</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>63297.31</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>210969757</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>68058.35000000001</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>-1411.56</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>68891.21000000001</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>69453.88</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>66445.78999999999</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>178027060</v>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="n">
+        <v>73299.02</v>
+      </c>
+      <c r="Y2" s="1" t="n">
+        <v>5240.67</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA2" s="1" t="n">
+        <v>68294.27</v>
+      </c>
+      <c r="AB2" s="1" t="n">
+        <v>74029.41</v>
+      </c>
+      <c r="AC2" s="1" t="n">
+        <v>67485.78</v>
+      </c>
+      <c r="AD2" s="3" t="n">
+        <v>319881950</v>
+      </c>
+      <c r="AE2" s="4" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="AI2" s="1" t="n">
+        <v>71128.7</v>
+      </c>
+      <c r="AJ2" s="1" t="n">
+        <v>-2170.32</v>
+      </c>
+      <c r="AK2" s="2" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="AL2" s="1" t="n">
+        <v>72727.3</v>
+      </c>
+      <c r="AM2" s="1" t="n">
+        <v>73448.67</v>
+      </c>
+      <c r="AN2" s="1" t="n">
+        <v>70726.36</v>
+      </c>
+      <c r="AO2" s="3" t="n">
+        <v>221805820</v>
+      </c>
+      <c r="AP2" s="4" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="AT2" s="1" t="n">
+        <v>68298.02</v>
+      </c>
+      <c r="AU2" s="1" t="n">
+        <v>-2830.68</v>
+      </c>
+      <c r="AV2" s="2" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="AW2" s="1" t="n">
+        <v>70824.7</v>
+      </c>
+      <c r="AX2" s="1" t="n">
+        <v>71338.12</v>
+      </c>
+      <c r="AY2" s="1" t="n">
+        <v>67770.50999999999</v>
+      </c>
+      <c r="AZ2" s="3" t="n">
+        <v>247710939</v>
+      </c>
+      <c r="BA2" s="4" t="inlineStr">
+        <is>
+          <t>03/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>97.87</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>97.77</v>
+      </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>99.06</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>98.43000000000001</v>
+      </c>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>17:38 ET</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>98.81</v>
+      </c>
+      <c r="Y3" s="1" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>99.11</v>
+      </c>
+      <c r="AB3" s="1" t="n">
+        <v>99.33</v>
+      </c>
+      <c r="AC3" s="1" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="AD3" s="3" t="n"/>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>17:38 ET</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="AI3" s="1" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="AJ3" s="1" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AK3" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AL3" s="1" t="n">
+        <v>98.77</v>
+      </c>
+      <c r="AM3" s="1" t="n">
+        <v>99.41</v>
+      </c>
+      <c r="AN3" s="1" t="n">
+        <v>98.67</v>
+      </c>
+      <c r="AO3" s="3" t="n"/>
+      <c r="AP3" s="4" t="inlineStr">
+        <is>
+          <t>17:38 ET</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="AT3" s="1" t="n">
+        <v>98.98999999999999</v>
+      </c>
+      <c r="AU3" s="1" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AV3" s="2" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AW3" s="1" t="n">
+        <v>99.01000000000001</v>
+      </c>
+      <c r="AX3" s="1" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="AY3" s="1" t="n">
+        <v>98.84</v>
+      </c>
+      <c r="AZ3" s="3" t="n"/>
+      <c r="BA3" s="4" t="inlineStr">
+        <is>
+          <t>03/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>0.87192</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>-0.00422</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0.87692</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>0.87876</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>0.87192</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>659475</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>0.86937</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>-0.00255</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>0.87192</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>0.8739400000000001</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>0.86913</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>721523</v>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>0.86996</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>0.00059</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>0.86937</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>0.8712800000000001</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>0.86859</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>635614</v>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="AI4" s="1" t="n">
+        <v>0.86908</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>-0.00088</v>
+      </c>
+      <c r="AK4" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>0.86997</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>0.87117</v>
+      </c>
+      <c r="AN4" s="1" t="n">
+        <v>0.8685</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>673394</v>
+      </c>
+      <c r="AP4" s="4" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="AT4" s="1" t="n">
+        <v>0.86599</v>
+      </c>
+      <c r="AU4" s="1" t="n">
+        <v>-0.00309</v>
+      </c>
+      <c r="AV4" s="2" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AW4" s="1" t="n">
+        <v>0.86907</v>
+      </c>
+      <c r="AX4" s="1" t="n">
+        <v>0.87024</v>
+      </c>
+      <c r="AY4" s="1" t="n">
+        <v>0.86577</v>
+      </c>
+      <c r="AZ4" s="3" t="n">
+        <v>669359</v>
+      </c>
+      <c r="BA4" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0.5528999999999999</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0.5397999999999999</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1052553</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0.5501</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>-0.0028</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0.5528999999999999</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>0.5554</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>0.5456</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>1227126</v>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>0.5513</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>0.5501</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>0.5528</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>1126801</v>
+      </c>
+      <c r="AE5" s="4" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="AI5" s="1" t="n">
+        <v>0.5472</v>
+      </c>
+      <c r="AJ5" s="1" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="AK5" s="2" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="AL5" s="1" t="n">
+        <v>0.5513</v>
+      </c>
+      <c r="AM5" s="1" t="n">
+        <v>0.5518999999999999</v>
+      </c>
+      <c r="AN5" s="1" t="n">
+        <v>0.5462</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>1161791</v>
+      </c>
+      <c r="AP5" s="4" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="AT5" s="1" t="n">
+        <v>0.5456</v>
+      </c>
+      <c r="AU5" s="1" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="AV5" s="2" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AW5" s="1" t="n">
+        <v>0.5472</v>
+      </c>
+      <c r="AX5" s="1" t="n">
+        <v>0.5499000000000001</v>
+      </c>
+      <c r="AY5" s="1" t="n">
+        <v>0.5445</v>
+      </c>
+      <c r="AZ5" s="3" t="n">
+        <v>1137993</v>
+      </c>
+      <c r="BA5" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>1.36757</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0.00326</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>1.36462</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>1.37185</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>1.36375</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>428316</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>1.36789</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0.00032</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>1.36757</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>1.3753</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>1.36533</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>510310</v>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>1.36435</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>-0.00354</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>1.36789</v>
+      </c>
+      <c r="AB6" s="1" t="n">
+        <v>1.37001</v>
+      </c>
+      <c r="AC6" s="1" t="n">
+        <v>1.36271</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>425707</v>
+      </c>
+      <c r="AE6" s="4" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="AI6" s="1" t="n">
+        <v>1.36752</v>
+      </c>
+      <c r="AJ6" s="1" t="n">
+        <v>0.00317</v>
+      </c>
+      <c r="AK6" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AL6" s="1" t="n">
+        <v>1.36435</v>
+      </c>
+      <c r="AM6" s="1" t="n">
+        <v>1.37164</v>
+      </c>
+      <c r="AN6" s="1" t="n">
+        <v>1.36158</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>458947</v>
+      </c>
+      <c r="AP6" s="4" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="AT6" s="1" t="n">
+        <v>1.35665</v>
+      </c>
+      <c r="AU6" s="1" t="n">
+        <v>-0.01087</v>
+      </c>
+      <c r="AV6" s="2" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="AW6" s="1" t="n">
+        <v>1.36751</v>
+      </c>
+      <c r="AX6" s="1" t="n">
+        <v>1.36817</v>
+      </c>
+      <c r="AY6" s="1" t="n">
+        <v>1.35636</v>
+      </c>
+      <c r="AZ6" s="3" t="n">
+        <v>441077</v>
+      </c>
+      <c r="BA6" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.97024</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>-0.00049</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.96233</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.97123</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.96055</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>440550</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.96241</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>-0.00783</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.97023</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.97309</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0.9546</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>522134</v>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>0.96539</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>0.00298</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>0.96241</v>
+      </c>
+      <c r="AB7" s="1" t="n">
+        <v>0.96692</v>
+      </c>
+      <c r="AC7" s="1" t="n">
+        <v>0.95653</v>
+      </c>
+      <c r="AD7" s="3" t="n">
+        <v>463028</v>
+      </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="AI7" s="1" t="n">
+        <v>0.95828</v>
+      </c>
+      <c r="AJ7" s="1" t="n">
+        <v>-0.00711</v>
+      </c>
+      <c r="AK7" s="2" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="AL7" s="1" t="n">
+        <v>0.96539</v>
+      </c>
+      <c r="AM7" s="1" t="n">
+        <v>0.96632</v>
+      </c>
+      <c r="AN7" s="1" t="n">
+        <v>0.95552</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>491451</v>
+      </c>
+      <c r="AP7" s="4" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="AT7" s="1" t="n">
+        <v>0.95384</v>
+      </c>
+      <c r="AU7" s="1" t="n">
+        <v>-0.00444</v>
+      </c>
+      <c r="AV7" s="2" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="AW7" s="1" t="n">
+        <v>0.95828</v>
+      </c>
+      <c r="AX7" s="1" t="n">
+        <v>0.9621</v>
+      </c>
+      <c r="AY7" s="1" t="n">
+        <v>0.95295</v>
+      </c>
+      <c r="AZ7" s="3" t="n">
+        <v>503620</v>
+      </c>
+      <c r="BA7" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="AB8" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="AC8" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="AD8" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="AE8" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="AI8" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="AJ8" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="AK8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AL8" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="AM8" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="AN8" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="AP8" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="AT8" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="AU8" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="AV8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AW8" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="AX8" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="AY8" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="AZ8" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="BA8" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="AB9" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="AC9" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="AD9" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="AI9" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="AJ9" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="AK9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AL9" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="AM9" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="AN9" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="AP9" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="AT9" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="AU9" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="AV9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AW9" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="AX9" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="AY9" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="AZ9" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="BA9" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>89.351</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>-4.72</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>93.914</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>96.393</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>86.599</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>209534</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>82.053</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>-7.298</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>-8.17</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>89.34999999999999</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>91.322</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>78.09099999999999</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>208906</v>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>83.539</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>1.486</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>82.054</v>
+      </c>
+      <c r="AB10" s="1" t="n">
+        <v>86.78400000000001</v>
+      </c>
+      <c r="AC10" s="1" t="n">
+        <v>81.733</v>
+      </c>
+      <c r="AD10" s="3" t="n">
+        <v>190288</v>
+      </c>
+      <c r="AE10" s="4" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="AI10" s="1" t="n">
+        <v>82.244</v>
+      </c>
+      <c r="AJ10" s="1" t="n">
+        <v>-1.295</v>
+      </c>
+      <c r="AK10" s="2" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="AL10" s="1" t="n">
+        <v>83.539</v>
+      </c>
+      <c r="AM10" s="1" t="n">
+        <v>85.541</v>
+      </c>
+      <c r="AN10" s="1" t="n">
+        <v>80.66200000000001</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>197948</v>
+      </c>
+      <c r="AP10" s="4" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="AT10" s="1" t="n">
+        <v>84.538</v>
+      </c>
+      <c r="AU10" s="1" t="n">
+        <v>2.294</v>
+      </c>
+      <c r="AV10" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AW10" s="1" t="n">
+        <v>82.24299999999999</v>
+      </c>
+      <c r="AX10" s="1" t="n">
+        <v>84.947</v>
+      </c>
+      <c r="AY10" s="1" t="n">
+        <v>81.652</v>
+      </c>
+      <c r="AZ10" s="3" t="n">
+        <v>187267</v>
+      </c>
+      <c r="BA10" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>5322.02</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>5281.55</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>5418.84</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>5262.89</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>188902</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>5088.38</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>-233.64</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>5322.02</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>5379.89</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>4997.76</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>201061</v>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>5141.35</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <v>5088.38</v>
+      </c>
+      <c r="AB11" s="1" t="n">
+        <v>5206.1</v>
+      </c>
+      <c r="AC11" s="1" t="n">
+        <v>5086.41</v>
+      </c>
+      <c r="AD11" s="3" t="n">
+        <v>180222</v>
+      </c>
+      <c r="AE11" s="4" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="AI11" s="1" t="n">
+        <v>5081.24</v>
+      </c>
+      <c r="AJ11" s="1" t="n">
+        <v>-60.11</v>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="AL11" s="1" t="n">
+        <v>5141.35</v>
+      </c>
+      <c r="AM11" s="1" t="n">
+        <v>5194.88</v>
+      </c>
+      <c r="AN11" s="1" t="n">
+        <v>5052.57</v>
+      </c>
+      <c r="AO11" s="3" t="n">
+        <v>173174</v>
+      </c>
+      <c r="AP11" s="4" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="AT11" s="1" t="n">
+        <v>5172.81</v>
+      </c>
+      <c r="AU11" s="1" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="AV11" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW11" s="1" t="n">
+        <v>5081.24</v>
+      </c>
+      <c r="AX11" s="1" t="n">
+        <v>5177.56</v>
+      </c>
+      <c r="AY11" s="1" t="n">
+        <v>5063.96</v>
+      </c>
+      <c r="AZ11" s="3" t="n">
+        <v>164349</v>
+      </c>
+      <c r="BA11" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>0.5699</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>0.5703</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>342284</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0.5716</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0.5699</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.5744</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.5693</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>375683</v>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AA12" s="1" t="n">
+        <v>0.5716</v>
+      </c>
+      <c r="AB12" s="1" t="n">
+        <v>0.5729</v>
+      </c>
+      <c r="AC12" s="1" t="n">
+        <v>0.5701000000000001</v>
+      </c>
+      <c r="AD12" s="3" t="n">
+        <v>346946</v>
+      </c>
+      <c r="AE12" s="4" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="AI12" s="1" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AJ12" s="1" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AL12" s="1" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="AM12" s="1" t="n">
+        <v>0.5731000000000001</v>
+      </c>
+      <c r="AN12" s="1" t="n">
+        <v>0.5706</v>
+      </c>
+      <c r="AO12" s="3" t="n">
+        <v>358962</v>
+      </c>
+      <c r="AP12" s="4" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="AT12" s="1" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="AU12" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AV12" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW12" s="1" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="AX12" s="1" t="n">
+        <v>0.5732</v>
+      </c>
+      <c r="AY12" s="1" t="n">
+        <v>0.5706</v>
+      </c>
+      <c r="AZ12" s="3" t="n">
+        <v>345147</v>
+      </c>
+      <c r="BA12" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>1.59884</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>-0.01321</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>1.60604</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>1.60933</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>1.59763</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>486167</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>1.58846</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>-0.01038</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>1.59882</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>1.59956</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>1.58374</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>523927</v>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>1.58739</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <v>-0.00108</v>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <v>1.58848</v>
+      </c>
+      <c r="AB13" s="1" t="n">
+        <v>1.59285</v>
+      </c>
+      <c r="AC13" s="1" t="n">
+        <v>1.58448</v>
+      </c>
+      <c r="AD13" s="3" t="n">
+        <v>470488</v>
+      </c>
+      <c r="AE13" s="4" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="AI13" s="1" t="n">
+        <v>1.58754</v>
+      </c>
+      <c r="AJ13" s="1" t="n">
+        <v>0.00015</v>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AL13" s="1" t="n">
+        <v>1.58738</v>
+      </c>
+      <c r="AM13" s="1" t="n">
+        <v>1.58807</v>
+      </c>
+      <c r="AN13" s="1" t="n">
+        <v>1.58139</v>
+      </c>
+      <c r="AO13" s="3" t="n">
+        <v>447812</v>
+      </c>
+      <c r="AP13" s="4" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="AT13" s="1" t="n">
+        <v>1.57593</v>
+      </c>
+      <c r="AU13" s="1" t="n">
+        <v>-0.01161</v>
+      </c>
+      <c r="AV13" s="2" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="AW13" s="1" t="n">
+        <v>1.58753</v>
+      </c>
+      <c r="AX13" s="1" t="n">
+        <v>1.58793</v>
+      </c>
+      <c r="AY13" s="1" t="n">
+        <v>1.57544</v>
+      </c>
+      <c r="AZ13" s="3" t="n">
+        <v>483330</v>
+      </c>
+      <c r="BA13" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>157.358</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>156.039</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>157.751</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>156.035</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>659484</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>157.728</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>157.358</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>157.968</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>157.151</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>708637</v>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>157.064</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>-0.664</v>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <v>157.729</v>
+      </c>
+      <c r="AB14" s="1" t="n">
+        <v>157.861</v>
+      </c>
+      <c r="AC14" s="1" t="n">
+        <v>156.857</v>
+      </c>
+      <c r="AD14" s="3" t="n">
+        <v>603232</v>
+      </c>
+      <c r="AE14" s="4" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="AI14" s="1" t="n">
+        <v>157.555</v>
+      </c>
+      <c r="AJ14" s="1" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AL14" s="1" t="n">
+        <v>157.063</v>
+      </c>
+      <c r="AM14" s="1" t="n">
+        <v>157.852</v>
+      </c>
+      <c r="AN14" s="1" t="n">
+        <v>156.461</v>
+      </c>
+      <c r="AO14" s="3" t="n">
+        <v>663002</v>
+      </c>
+      <c r="AP14" s="4" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="AT14" s="1" t="n">
+        <v>157.791</v>
+      </c>
+      <c r="AU14" s="1" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="AV14" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AW14" s="1" t="n">
+        <v>157.556</v>
+      </c>
+      <c r="AX14" s="1" t="n">
+        <v>158.088</v>
+      </c>
+      <c r="AY14" s="1" t="n">
+        <v>157.394</v>
+      </c>
+      <c r="AZ14" s="3" t="n">
+        <v>635552</v>
+      </c>
+      <c r="BA14" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>0.91108</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.00216</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>0.90291</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>0.91308</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>0.90291</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>504498</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>0.90801</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>-0.00307</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>0.91107</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>0.91278</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>0.9067</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>592234</v>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>0.90651</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="Z15" s="2" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>0.90803</v>
+      </c>
+      <c r="AB15" s="1" t="n">
+        <v>0.90989</v>
+      </c>
+      <c r="AC15" s="1" t="n">
+        <v>0.90564</v>
+      </c>
+      <c r="AD15" s="3" t="n">
+        <v>502977</v>
+      </c>
+      <c r="AE15" s="4" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="AI15" s="1" t="n">
+        <v>0.9065800000000001</v>
+      </c>
+      <c r="AJ15" s="1" t="n">
+        <v>6.999999999999999e-05</v>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AL15" s="1" t="n">
+        <v>0.9065800000000001</v>
+      </c>
+      <c r="AM15" s="1" t="n">
+        <v>0.90725</v>
+      </c>
+      <c r="AN15" s="1" t="n">
+        <v>0.90499</v>
+      </c>
+      <c r="AO15" s="3" t="n">
+        <v>543713</v>
+      </c>
+      <c r="AP15" s="4" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="AT15" s="1" t="n">
+        <v>0.90162</v>
+      </c>
+      <c r="AU15" s="1" t="n">
+        <v>-0.00496</v>
+      </c>
+      <c r="AV15" s="2" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="AW15" s="1" t="n">
+        <v>0.90655</v>
+      </c>
+      <c r="AX15" s="1" t="n">
+        <v>0.9069700000000001</v>
+      </c>
+      <c r="AY15" s="1" t="n">
+        <v>0.9009</v>
+      </c>
+      <c r="AZ15" s="3" t="n">
+        <v>522437</v>
+      </c>
+      <c r="BA15" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>0.7794</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.009950000000000001</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>0.7675</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.78137</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>0.76742</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>468898</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>03/02/26</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>0.7819199999999999</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0.00251</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>0.77941</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>0.78787</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>0.7784799999999999</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>541402</v>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>03/03/26</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>0.77913</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>-0.00279</v>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AA16" s="1" t="n">
+        <v>0.78191</v>
+      </c>
+      <c r="AB16" s="1" t="n">
+        <v>0.78352</v>
+      </c>
+      <c r="AC16" s="1" t="n">
+        <v>0.77873</v>
+      </c>
+      <c r="AD16" s="3" t="n">
+        <v>455291</v>
+      </c>
+      <c r="AE16" s="4" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="AI16" s="1" t="n">
+        <v>0.78091</v>
+      </c>
+      <c r="AJ16" s="1" t="n">
+        <v>0.00178</v>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AL16" s="1" t="n">
+        <v>0.77913</v>
+      </c>
+      <c r="AM16" s="1" t="n">
+        <v>0.78377</v>
+      </c>
+      <c r="AN16" s="1" t="n">
+        <v>0.77826</v>
+      </c>
+      <c r="AO16" s="3" t="n">
+        <v>493344</v>
+      </c>
+      <c r="AP16" s="4" t="inlineStr">
+        <is>
+          <t>03/05/26</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="AT16" s="1" t="n">
+        <v>0.77606</v>
+      </c>
+      <c r="AU16" s="1" t="n">
+        <v>-0.00485</v>
+      </c>
+      <c r="AV16" s="2" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="AW16" s="1" t="n">
+        <v>0.7809199999999999</v>
+      </c>
+      <c r="AX16" s="1" t="n">
+        <v>0.7827499999999999</v>
+      </c>
+      <c r="AY16" s="1" t="n">
+        <v>0.77586</v>
+      </c>
+      <c r="AZ16" s="3" t="n">
+        <v>477340</v>
+      </c>
+      <c r="BA16" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -521,29 +3108,29 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>69469.91</v>
+        <v>68827.97</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>3938.81</v>
+        <v>529.95</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6.01</v>
+        <v>0.78</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>65712.14</v>
+        <v>65962.62</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>69995.41</v>
+        <v>69499.98</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>63297.31</v>
+        <v>65648.89</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>210969757</v>
+        <v>243109918</v>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>03/02/26</t>
+          <t>03/09/26</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -552,29 +3139,29 @@
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>68058.35000000001</v>
+        <v>70229.21000000001</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>-1411.56</v>
+        <v>1401.24</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>-2.03</v>
+        <v>2.04</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>68891.21000000001</v>
+        <v>68397.36</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>69453.88</v>
+        <v>71606.47</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>66445.78999999999</v>
+        <v>68395.47</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>178027060</v>
+        <v>294001418</v>
       </c>
       <c r="T2" s="4" t="inlineStr">
         <is>
-          <t>03/03/26</t>
+          <t>03/10/26</t>
         </is>
       </c>
     </row>
@@ -585,27 +3172,27 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>98.56</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0.95</v>
+        <v>-0.25</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.97</v>
+        <v>-0.25</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>97.87</v>
+        <v>99.33</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>98.75</v>
+        <v>99.69</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>97.77</v>
+        <v>98.72</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>03/03/26</t>
+          <t>17:39 ET</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -614,27 +3201,27 @@
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>99.06</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>0.68</v>
+        <v>-0.25</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>98.56</v>
+        <v>98.86</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>99.68000000000001</v>
+        <v>98.95</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>98.43000000000001</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>17:38 ET</t>
+          <t>17:39 ET</t>
         </is>
       </c>
     </row>
@@ -645,29 +3232,29 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>0.87192</v>
+        <v>0.86583</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>-0.00422</v>
+        <v>-0.00016</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.02</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.87692</v>
+        <v>0.86602</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.87876</v>
+        <v>0.86769</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.87192</v>
+        <v>0.86441</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>659475</v>
+        <v>741681</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>03/02/26</t>
+          <t>03/09/26</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -676,29 +3263,29 @@
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>0.86937</v>
+        <v>0.86531</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>-0.00255</v>
+        <v>-0.00052</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.06</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>0.87192</v>
+        <v>0.86583</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>0.8739400000000001</v>
+        <v>0.86617</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>0.86913</v>
+        <v>0.86422</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>721523</v>
+        <v>650594</v>
       </c>
       <c r="T4" s="4" t="inlineStr">
         <is>
-          <t>03/03/26</t>
+          <t>03/10/26</t>
         </is>
       </c>
     </row>
@@ -709,29 +3296,29 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.0054</v>
+        <v>0.0044</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.5413</v>
+        <v>0.5446</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.553</v>
+        <v>0.5507</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1052553</v>
+        <v>1278155</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>03/02/26</t>
+          <t>03/09/26</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -740,29 +3327,29 @@
         </is>
       </c>
       <c r="M5" s="1" t="n">
-        <v>0.5501</v>
+        <v>0.5543</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>-0.0028</v>
+        <v>0.0043</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-0.51</v>
+        <v>0.78</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>0.5554</v>
+        <v>0.556</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>0.5456</v>
+        <v>0.5487</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1227126</v>
+        <v>1129256</v>
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>03/03/26</t>
+          <t>03/10/26</t>
         </is>
       </c>
     </row>
@@ -773,29 +3360,29 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>1.36757</v>
+        <v>1.35876</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>0.00326</v>
+        <v>0.00211</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.36462</v>
+        <v>1.3602</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1.37185</v>
+        <v>1.36065</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>1.36375</v>
+        <v>1.35257</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>428316</v>
+        <v>515665</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>03/02/26</t>
+          <t>03/09/26</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -804,29 +3391,29 @@
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>1.36789</v>
+        <v>1.35802</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>0.00032</v>
+        <v>-0.00074</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>1.36757</v>
+        <v>1.35876</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>1.3753</v>
+        <v>1.36016</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>1.36533</v>
+        <v>1.35422</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>510310</v>
+        <v>423423</v>
       </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t>03/03/26</t>
+          <t>03/10/26</t>
         </is>
       </c>
     </row>
@@ -837,29 +3424,29 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.97024</v>
+        <v>0.96144</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>-0.00049</v>
+        <v>0.0076</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.8</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.96233</v>
+        <v>0.95026</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.97123</v>
+        <v>0.9618100000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.96055</v>
+        <v>0.9463200000000001</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>440550</v>
+        <v>569484</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>03/02/26</t>
+          <t>03/09/26</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -868,29 +3455,29 @@
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.96241</v>
+        <v>0.96687</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>-0.00783</v>
+        <v>0.00543</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>0.97023</v>
+        <v>0.96144</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.97309</v>
+        <v>0.97275</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>0.9546</v>
+        <v>0.95916</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>522134</v>
+        <v>495187</v>
       </c>
       <c r="T7" s="4" t="inlineStr">
         <is>
-          <t>03/03/26</t>
+          <t>03/10/26</t>
         </is>
       </c>
     </row>
@@ -1029,29 +3616,29 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>89.351</v>
+        <v>87.006</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>-4.43</v>
+        <v>2.468</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-4.72</v>
+        <v>2.92</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>93.914</v>
+        <v>84.547</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>96.393</v>
+        <v>87.011</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>86.599</v>
+        <v>79.767</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>209534</v>
+        <v>207120</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>03/02/26</t>
+          <t>03/09/26</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1060,29 +3647,29 @@
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>82.053</v>
+        <v>88.343</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>-7.298</v>
+        <v>1.337</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>-8.17</v>
+        <v>1.54</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>89.34999999999999</v>
+        <v>87.006</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>91.322</v>
+        <v>89.989</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>78.09099999999999</v>
+        <v>86.68600000000001</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>208906</v>
+        <v>185201</v>
       </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
-          <t>03/03/26</t>
+          <t>03/10/26</t>
         </is>
       </c>
     </row>
@@ -1093,29 +3680,29 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>5322.02</v>
+        <v>5136.97</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>43.7</v>
+        <v>-35.85</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.83</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>5281.55</v>
+        <v>5173.87</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>5418.84</v>
+        <v>5190.45</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>5262.89</v>
+        <v>5016.24</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>188902</v>
+        <v>197700</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>03/02/26</t>
+          <t>03/09/26</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1124,29 +3711,29 @@
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>5088.38</v>
+        <v>5192.89</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>-233.64</v>
+        <v>55.92</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>-4.39</v>
+        <v>1.09</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>5322.02</v>
+        <v>5136.97</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>5379.89</v>
+        <v>5238.44</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>4997.76</v>
+        <v>5119.93</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>201061</v>
+        <v>169037</v>
       </c>
       <c r="T11" s="4" t="inlineStr">
         <is>
-          <t>03/03/26</t>
+          <t>03/10/26</t>
         </is>
       </c>
     </row>
@@ -1157,29 +3744,29 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.5699</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>0.0059</v>
+        <v>0.0001</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1.05</v>
+        <v>0.02</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.5625</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.5703</v>
+        <v>0.5763</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.572</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>342284</v>
+        <v>386283</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>03/02/26</t>
+          <t>03/09/26</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1188,29 +3775,29 @@
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0.5716</v>
+        <v>0.5733</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>0.0017</v>
+        <v>0.0012</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>0.5699</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.5744</v>
+        <v>0.5737</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.5693</v>
+        <v>0.5709</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>375683</v>
+        <v>337701</v>
       </c>
       <c r="T12" s="4" t="inlineStr">
         <is>
-          <t>03/03/26</t>
+          <t>03/10/26</t>
         </is>
       </c>
     </row>
@@ -1221,29 +3808,29 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>1.59884</v>
+        <v>1.581</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>-0.01321</v>
+        <v>0.00507</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>-0.82</v>
+        <v>0.32</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>1.60604</v>
+        <v>1.57548</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>1.60933</v>
+        <v>1.58119</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>1.59763</v>
+        <v>1.56133</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>486167</v>
+        <v>549440</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>03/02/26</t>
+          <t>03/09/26</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1252,29 +3839,29 @@
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>1.58846</v>
+        <v>1.57672</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>-0.01038</v>
+        <v>-0.00428</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>-0.65</v>
+        <v>-0.27</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>1.59882</v>
+        <v>1.58099</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>1.59956</v>
+        <v>1.5835</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>1.58374</v>
+        <v>1.57523</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>523927</v>
+        <v>469804</v>
       </c>
       <c r="T13" s="4" t="inlineStr">
         <is>
-          <t>03/03/26</t>
+          <t>03/10/26</t>
         </is>
       </c>
     </row>
@@ -1285,29 +3872,29 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>157.358</v>
+        <v>157.666</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>1.302</v>
+        <v>-0.125</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.83</v>
+        <v>-0.08</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>156.039</v>
+        <v>157.965</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>157.751</v>
+        <v>158.899</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>156.035</v>
+        <v>157.634</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>659484</v>
+        <v>711381</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>03/02/26</t>
+          <t>03/09/26</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1316,29 +3903,29 @@
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>157.728</v>
+        <v>158.053</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>0.37</v>
+        <v>0.387</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>157.358</v>
+        <v>157.669</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>157.968</v>
+        <v>158.123</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>157.151</v>
+        <v>157.275</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>708637</v>
+        <v>650791</v>
       </c>
       <c r="T14" s="4" t="inlineStr">
         <is>
-          <t>03/03/26</t>
+          <t>03/10/26</t>
         </is>
       </c>
     </row>
@@ -1349,29 +3936,29 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0.91108</v>
+        <v>0.90452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>0.00216</v>
+        <v>0.0029</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0.90291</v>
+        <v>0.90119</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.91308</v>
+        <v>0.90455</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>0.90291</v>
+        <v>0.8981</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>504498</v>
+        <v>615896</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>03/02/26</t>
+          <t>03/09/26</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1380,29 +3967,29 @@
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.90801</v>
+        <v>0.90395</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>-0.00307</v>
+        <v>-0.00057</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.06</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>0.91107</v>
+        <v>0.90452</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.91278</v>
+        <v>0.90504</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.9067</v>
+        <v>0.90235</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>592234</v>
+        <v>544880</v>
       </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
-          <t>03/03/26</t>
+          <t>03/10/26</t>
         </is>
       </c>
     </row>
@@ -1413,29 +4000,29 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0.7794</v>
+        <v>0.77733</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>0.009950000000000001</v>
+        <v>0.00127</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1.29</v>
+        <v>0.16</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.7675</v>
+        <v>0.7799</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.78137</v>
+        <v>0.78256</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.76742</v>
+        <v>0.77697</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>468898</v>
+        <v>552421</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>03/02/26</t>
+          <t>03/09/26</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1444,29 +4031,29 @@
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.7819199999999999</v>
+        <v>0.77856</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>0.00251</v>
+        <v>0.00123</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0.32</v>
+        <v>0.16</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>0.77941</v>
+        <v>0.77734</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.78787</v>
+        <v>0.77919</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.7784799999999999</v>
+        <v>0.77481</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>541402</v>
+        <v>466475</v>
       </c>
       <c r="T16" s="4" t="inlineStr">
         <is>
-          <t>03/03/26</t>
+          <t>03/10/26</t>
         </is>
       </c>
     </row>

--- a/outputs/march.xlsx
+++ b/outputs/march.xlsx
@@ -3006,7 +3006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:AE16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3100,6 +3100,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3164,6 +3209,37 @@
           <t>03/10/26</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="n">
+        <v>70489.89999999999</v>
+      </c>
+      <c r="Y2" s="1" t="n">
+        <v>260.69</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AA2" s="1" t="n">
+        <v>70229.21000000001</v>
+      </c>
+      <c r="AB2" s="1" t="n">
+        <v>71234.03</v>
+      </c>
+      <c r="AC2" s="1" t="n">
+        <v>69014.31</v>
+      </c>
+      <c r="AD2" s="3" t="n">
+        <v>194538928</v>
+      </c>
+      <c r="AE2" s="4" t="inlineStr">
+        <is>
+          <t>15:44 CT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3224,6 +3300,37 @@
           <t>17:39 ET</t>
         </is>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="Y3" s="1" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="AB3" s="1" t="n">
+        <v>99.29000000000001</v>
+      </c>
+      <c r="AC3" s="1" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>17:29 ET</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3288,6 +3395,37 @@
           <t>03/10/26</t>
         </is>
       </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>0.8623499999999999</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>-0.00296</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>0.86531</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>0.86573</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>0.86221</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>577383</v>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>15:44 CT</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3352,6 +3490,37 @@
           <t>03/10/26</t>
         </is>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>0.5581</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>0.5543</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>0.5596</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>0.5537</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>974808</v>
+      </c>
+      <c r="AE5" s="4" t="inlineStr">
+        <is>
+          <t>15:44 CT</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3416,6 +3585,37 @@
           <t>03/10/26</t>
         </is>
       </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>1.35929</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>0.00126</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>1.35803</v>
+      </c>
+      <c r="AB6" s="1" t="n">
+        <v>1.3605</v>
+      </c>
+      <c r="AC6" s="1" t="n">
+        <v>1.3555</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>362847</v>
+      </c>
+      <c r="AE6" s="4" t="inlineStr">
+        <is>
+          <t>15:44 CT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3480,6 +3680,37 @@
           <t>03/10/26</t>
         </is>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>0.97201</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>0.00514</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>0.96687</v>
+      </c>
+      <c r="AB7" s="1" t="n">
+        <v>0.97598</v>
+      </c>
+      <c r="AC7" s="1" t="n">
+        <v>0.96619</v>
+      </c>
+      <c r="AD7" s="3" t="n">
+        <v>432646</v>
+      </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>15:44 CT</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3544,6 +3775,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="AB8" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="AC8" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="AD8" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="AE8" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3608,6 +3870,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="AB9" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="AC9" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="AD9" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3672,6 +3965,37 @@
           <t>03/10/26</t>
         </is>
       </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>85.69499999999999</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>-2.648</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>88.34099999999999</v>
+      </c>
+      <c r="AB10" s="1" t="n">
+        <v>90.98</v>
+      </c>
+      <c r="AC10" s="1" t="n">
+        <v>84.491</v>
+      </c>
+      <c r="AD10" s="3" t="n">
+        <v>179483</v>
+      </c>
+      <c r="AE10" s="4" t="inlineStr">
+        <is>
+          <t>15:44 CT</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3736,6 +4060,37 @@
           <t>03/10/26</t>
         </is>
       </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>5176.2</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>-16.69</v>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <v>5192.93</v>
+      </c>
+      <c r="AB11" s="1" t="n">
+        <v>5222.92</v>
+      </c>
+      <c r="AC11" s="1" t="n">
+        <v>5152.02</v>
+      </c>
+      <c r="AD11" s="3" t="n">
+        <v>146056</v>
+      </c>
+      <c r="AE11" s="4" t="inlineStr">
+        <is>
+          <t>15:44 CT</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3800,6 +4155,37 @@
           <t>03/10/26</t>
         </is>
       </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>0.5741000000000001</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AA12" s="1" t="n">
+        <v>0.5733</v>
+      </c>
+      <c r="AB12" s="1" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="AC12" s="1" t="n">
+        <v>0.5725</v>
+      </c>
+      <c r="AD12" s="3" t="n">
+        <v>295744</v>
+      </c>
+      <c r="AE12" s="4" t="inlineStr">
+        <is>
+          <t>15:44 CT</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3864,6 +4250,37 @@
           <t>03/10/26</t>
         </is>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>1.57216</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <v>-0.00456</v>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <v>1.57673</v>
+      </c>
+      <c r="AB13" s="1" t="n">
+        <v>1.57944</v>
+      </c>
+      <c r="AC13" s="1" t="n">
+        <v>1.57049</v>
+      </c>
+      <c r="AD13" s="3" t="n">
+        <v>412273</v>
+      </c>
+      <c r="AE13" s="4" t="inlineStr">
+        <is>
+          <t>15:44 CT</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3928,6 +4345,37 @@
           <t>03/10/26</t>
         </is>
       </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>158.961</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <v>158.053</v>
+      </c>
+      <c r="AB14" s="1" t="n">
+        <v>158.975</v>
+      </c>
+      <c r="AC14" s="1" t="n">
+        <v>157.864</v>
+      </c>
+      <c r="AD14" s="3" t="n">
+        <v>544357</v>
+      </c>
+      <c r="AE14" s="4" t="inlineStr">
+        <is>
+          <t>15:44 CT</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3992,6 +4440,37 @@
           <t>03/10/26</t>
         </is>
       </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>0.90261</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>-0.00134</v>
+      </c>
+      <c r="Z15" s="2" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>0.90395</v>
+      </c>
+      <c r="AB15" s="1" t="n">
+        <v>0.90473</v>
+      </c>
+      <c r="AC15" s="1" t="n">
+        <v>0.90097</v>
+      </c>
+      <c r="AD15" s="3" t="n">
+        <v>453504</v>
+      </c>
+      <c r="AE15" s="4" t="inlineStr">
+        <is>
+          <t>15:44 CT</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4054,6 +4533,37 @@
       <c r="T16" s="4" t="inlineStr">
         <is>
           <t>03/10/26</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>0.78038</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>0.00182</v>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AA16" s="1" t="n">
+        <v>0.77858</v>
+      </c>
+      <c r="AB16" s="1" t="n">
+        <v>0.78086</v>
+      </c>
+      <c r="AC16" s="1" t="n">
+        <v>0.77657</v>
+      </c>
+      <c r="AD16" s="3" t="n">
+        <v>399200</v>
+      </c>
+      <c r="AE16" s="4" t="inlineStr">
+        <is>
+          <t>15:44 CT</t>
         </is>
       </c>
     </row>

--- a/outputs/march.xlsx
+++ b/outputs/march.xlsx
@@ -3006,7 +3006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE16"/>
+  <dimension ref="A1:AP16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3145,6 +3145,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3240,6 +3285,37 @@
           <t>15:44 CT</t>
         </is>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="AI2" s="1" t="n">
+        <v>70176.52</v>
+      </c>
+      <c r="AJ2" s="1" t="n">
+        <v>-490.74</v>
+      </c>
+      <c r="AK2" s="2" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="AL2" s="1" t="n">
+        <v>70199.71000000001</v>
+      </c>
+      <c r="AM2" s="1" t="n">
+        <v>70804.49000000001</v>
+      </c>
+      <c r="AN2" s="1" t="n">
+        <v>69228.64</v>
+      </c>
+      <c r="AO2" s="3" t="n">
+        <v>222050216</v>
+      </c>
+      <c r="AP2" s="4" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3331,6 +3407,37 @@
           <t>17:29 ET</t>
         </is>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="AI3" s="1" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="AJ3" s="1" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AK3" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AL3" s="1" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="AM3" s="1" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="AN3" s="1" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="AO3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="AP3" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3426,6 +3533,37 @@
           <t>15:44 CT</t>
         </is>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="AI4" s="1" t="n">
+        <v>0.86274</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>0.00028</v>
+      </c>
+      <c r="AK4" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>0.86246</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>0.86371</v>
+      </c>
+      <c r="AN4" s="1" t="n">
+        <v>0.86176</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>586557</v>
+      </c>
+      <c r="AP4" s="4" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3521,6 +3659,37 @@
           <t>15:44 CT</t>
         </is>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="AI5" s="1" t="n">
+        <v>0.5563</v>
+      </c>
+      <c r="AJ5" s="1" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="AK5" s="2" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AL5" s="1" t="n">
+        <v>0.5582</v>
+      </c>
+      <c r="AM5" s="1" t="n">
+        <v>0.5592</v>
+      </c>
+      <c r="AN5" s="1" t="n">
+        <v>0.5548</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>1016398</v>
+      </c>
+      <c r="AP5" s="4" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3616,6 +3785,37 @@
           <t>15:44 CT</t>
         </is>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="AI6" s="1" t="n">
+        <v>1.36415</v>
+      </c>
+      <c r="AJ6" s="1" t="n">
+        <v>0.00486</v>
+      </c>
+      <c r="AK6" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AL6" s="1" t="n">
+        <v>1.35928</v>
+      </c>
+      <c r="AM6" s="1" t="n">
+        <v>1.36427</v>
+      </c>
+      <c r="AN6" s="1" t="n">
+        <v>1.35769</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>385174</v>
+      </c>
+      <c r="AP6" s="4" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3711,6 +3911,37 @@
           <t>15:44 CT</t>
         </is>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="AI7" s="1" t="n">
+        <v>0.96538</v>
+      </c>
+      <c r="AJ7" s="1" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="AK7" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AL7" s="1" t="n">
+        <v>0.97218</v>
+      </c>
+      <c r="AM7" s="1" t="n">
+        <v>0.9729</v>
+      </c>
+      <c r="AN7" s="1" t="n">
+        <v>0.96378</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>444093</v>
+      </c>
+      <c r="AP7" s="4" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3806,6 +4037,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="AI8" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="AJ8" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="AK8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AL8" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="AM8" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="AN8" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="AP8" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3901,6 +4163,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="AI9" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="AJ9" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="AK9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AL9" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="AM9" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="AN9" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="AP9" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3996,6 +4289,37 @@
           <t>15:44 CT</t>
         </is>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="AI10" s="1" t="n">
+        <v>83.866</v>
+      </c>
+      <c r="AJ10" s="1" t="n">
+        <v>-1.881</v>
+      </c>
+      <c r="AK10" s="2" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="AL10" s="1" t="n">
+        <v>85.748</v>
+      </c>
+      <c r="AM10" s="1" t="n">
+        <v>87.437</v>
+      </c>
+      <c r="AN10" s="1" t="n">
+        <v>83.075</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>190620</v>
+      </c>
+      <c r="AP10" s="4" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4091,6 +4415,37 @@
           <t>15:44 CT</t>
         </is>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="AI11" s="1" t="n">
+        <v>5079.07</v>
+      </c>
+      <c r="AJ11" s="1" t="n">
+        <v>-96.89</v>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="AL11" s="1" t="n">
+        <v>5175.97</v>
+      </c>
+      <c r="AM11" s="1" t="n">
+        <v>5191.76</v>
+      </c>
+      <c r="AN11" s="1" t="n">
+        <v>5056.34</v>
+      </c>
+      <c r="AO11" s="3" t="n">
+        <v>166635</v>
+      </c>
+      <c r="AP11" s="4" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4186,6 +4541,37 @@
           <t>15:44 CT</t>
         </is>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="AI12" s="1" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="AJ12" s="1" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AL12" s="1" t="n">
+        <v>0.5742</v>
+      </c>
+      <c r="AM12" s="1" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="AN12" s="1" t="n">
+        <v>0.5735</v>
+      </c>
+      <c r="AO12" s="3" t="n">
+        <v>305873</v>
+      </c>
+      <c r="AP12" s="4" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4281,6 +4667,37 @@
           <t>15:44 CT</t>
         </is>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="AI13" s="1" t="n">
+        <v>1.56999</v>
+      </c>
+      <c r="AJ13" s="1" t="n">
+        <v>-0.00232</v>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AL13" s="1" t="n">
+        <v>1.57231</v>
+      </c>
+      <c r="AM13" s="1" t="n">
+        <v>1.57276</v>
+      </c>
+      <c r="AN13" s="1" t="n">
+        <v>1.56681</v>
+      </c>
+      <c r="AO13" s="3" t="n">
+        <v>402632</v>
+      </c>
+      <c r="AP13" s="4" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4376,6 +4793,37 @@
           <t>15:44 CT</t>
         </is>
       </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="AI14" s="1" t="n">
+        <v>159.35</v>
+      </c>
+      <c r="AJ14" s="1" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AL14" s="1" t="n">
+        <v>158.949</v>
+      </c>
+      <c r="AM14" s="1" t="n">
+        <v>159.432</v>
+      </c>
+      <c r="AN14" s="1" t="n">
+        <v>158.573</v>
+      </c>
+      <c r="AO14" s="3" t="n">
+        <v>568811</v>
+      </c>
+      <c r="AP14" s="4" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4471,6 +4919,37 @@
           <t>15:44 CT</t>
         </is>
       </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="AI15" s="1" t="n">
+        <v>0.90491</v>
+      </c>
+      <c r="AJ15" s="1" t="n">
+        <v>0.00207</v>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AL15" s="1" t="n">
+        <v>0.90285</v>
+      </c>
+      <c r="AM15" s="1" t="n">
+        <v>0.9051900000000001</v>
+      </c>
+      <c r="AN15" s="1" t="n">
+        <v>0.90186</v>
+      </c>
+      <c r="AO15" s="3" t="n">
+        <v>464129</v>
+      </c>
+      <c r="AP15" s="4" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4564,6 +5043,37 @@
       <c r="AE16" s="4" t="inlineStr">
         <is>
           <t>15:44 CT</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="AI16" s="1" t="n">
+        <v>0.78609</v>
+      </c>
+      <c r="AJ16" s="1" t="n">
+        <v>0.00557</v>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AL16" s="1" t="n">
+        <v>0.78052</v>
+      </c>
+      <c r="AM16" s="1" t="n">
+        <v>0.78638</v>
+      </c>
+      <c r="AN16" s="1" t="n">
+        <v>0.77977</v>
+      </c>
+      <c r="AO16" s="3" t="n">
+        <v>393237</v>
+      </c>
+      <c r="AP16" s="4" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
         </is>
       </c>
     </row>

--- a/outputs/march.xlsx
+++ b/outputs/march.xlsx
@@ -3006,7 +3006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP16"/>
+  <dimension ref="A1:BA16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3190,6 +3190,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3316,6 +3361,37 @@
           <t>03/12/26</t>
         </is>
       </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="AT2" s="1" t="n">
+        <v>71363.55</v>
+      </c>
+      <c r="AU2" s="1" t="n">
+        <v>1187.03</v>
+      </c>
+      <c r="AV2" s="2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AW2" s="1" t="n">
+        <v>70529.31</v>
+      </c>
+      <c r="AX2" s="1" t="n">
+        <v>73880</v>
+      </c>
+      <c r="AY2" s="1" t="n">
+        <v>70025.12</v>
+      </c>
+      <c r="AZ2" s="3" t="n">
+        <v>326017892</v>
+      </c>
+      <c r="BA2" s="4" t="inlineStr">
+        <is>
+          <t>03/13/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3430,12 +3506,41 @@
       <c r="AN3" s="1" t="n">
         <v>99.25</v>
       </c>
-      <c r="AO3" s="3" t="n">
+      <c r="AO3" s="3" t="n"/>
+      <c r="AP3" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="AT3" s="1" t="n">
+        <v>100.36</v>
+      </c>
+      <c r="AU3" s="1" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AV3" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AW3" s="1" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="AX3" s="1" t="n">
+        <v>100.54</v>
+      </c>
+      <c r="AY3" s="1" t="n">
+        <v>99.59</v>
+      </c>
+      <c r="AZ3" s="3" t="n">
         <v/>
       </c>
-      <c r="AP3" s="4" t="inlineStr">
-        <is>
-          <t>17:39 ET</t>
+      <c r="BA3" s="4" t="inlineStr">
+        <is>
+          <t>03/13/26</t>
         </is>
       </c>
     </row>
@@ -3564,6 +3669,37 @@
           <t>03/12/26</t>
         </is>
       </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="AT4" s="1" t="n">
+        <v>0.86347</v>
+      </c>
+      <c r="AU4" s="1" t="n">
+        <v>0.00073</v>
+      </c>
+      <c r="AV4" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW4" s="1" t="n">
+        <v>0.86274</v>
+      </c>
+      <c r="AX4" s="1" t="n">
+        <v>0.86546</v>
+      </c>
+      <c r="AY4" s="1" t="n">
+        <v>0.86202</v>
+      </c>
+      <c r="AZ4" s="3" t="n">
+        <v>609624</v>
+      </c>
+      <c r="BA4" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3690,6 +3826,37 @@
           <t>03/12/26</t>
         </is>
       </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="AT5" s="1" t="n">
+        <v>0.5523</v>
+      </c>
+      <c r="AU5" s="1" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="AV5" s="2" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="AW5" s="1" t="n">
+        <v>0.5563</v>
+      </c>
+      <c r="AX5" s="1" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="AY5" s="1" t="n">
+        <v>0.5523</v>
+      </c>
+      <c r="AZ5" s="3" t="n">
+        <v>1050876</v>
+      </c>
+      <c r="BA5" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3816,6 +3983,37 @@
           <t>03/12/26</t>
         </is>
       </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="AT6" s="1" t="n">
+        <v>1.37173</v>
+      </c>
+      <c r="AU6" s="1" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="AV6" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AW6" s="1" t="n">
+        <v>1.36414</v>
+      </c>
+      <c r="AX6" s="1" t="n">
+        <v>1.37416</v>
+      </c>
+      <c r="AY6" s="1" t="n">
+        <v>1.36214</v>
+      </c>
+      <c r="AZ6" s="3" t="n">
+        <v>392997</v>
+      </c>
+      <c r="BA6" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3942,6 +4140,37 @@
           <t>03/12/26</t>
         </is>
       </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="AT7" s="1" t="n">
+        <v>0.9575399999999999</v>
+      </c>
+      <c r="AU7" s="1" t="n">
+        <v>-0.00784</v>
+      </c>
+      <c r="AV7" s="2" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AW7" s="1" t="n">
+        <v>0.96539</v>
+      </c>
+      <c r="AX7" s="1" t="n">
+        <v>0.96705</v>
+      </c>
+      <c r="AY7" s="1" t="n">
+        <v>0.95743</v>
+      </c>
+      <c r="AZ7" s="3" t="n">
+        <v>454304</v>
+      </c>
+      <c r="BA7" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4068,6 +4297,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="AT8" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="AU8" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="AV8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AW8" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="AX8" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="AY8" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="AZ8" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="BA8" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4194,6 +4454,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="AT9" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="AU9" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="AV9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AW9" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="AX9" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="AY9" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="AZ9" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="BA9" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4320,6 +4611,37 @@
           <t>03/12/26</t>
         </is>
       </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="AT10" s="1" t="n">
+        <v>80.611</v>
+      </c>
+      <c r="AU10" s="1" t="n">
+        <v>-3.255</v>
+      </c>
+      <c r="AV10" s="2" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="AW10" s="1" t="n">
+        <v>83.866</v>
+      </c>
+      <c r="AX10" s="1" t="n">
+        <v>85.443</v>
+      </c>
+      <c r="AY10" s="1" t="n">
+        <v>79.51900000000001</v>
+      </c>
+      <c r="AZ10" s="3" t="n">
+        <v>198532</v>
+      </c>
+      <c r="BA10" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4446,6 +4768,37 @@
           <t>03/12/26</t>
         </is>
       </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="AT11" s="1" t="n">
+        <v>5019.98</v>
+      </c>
+      <c r="AU11" s="1" t="n">
+        <v>-59.09</v>
+      </c>
+      <c r="AV11" s="2" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="AW11" s="1" t="n">
+        <v>5079.11</v>
+      </c>
+      <c r="AX11" s="1" t="n">
+        <v>5128.25</v>
+      </c>
+      <c r="AY11" s="1" t="n">
+        <v>5009.88</v>
+      </c>
+      <c r="AZ11" s="3" t="n">
+        <v>167173</v>
+      </c>
+      <c r="BA11" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4572,6 +4925,37 @@
           <t>03/12/26</t>
         </is>
       </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="AT12" s="1" t="n">
+        <v>0.5768</v>
+      </c>
+      <c r="AU12" s="1" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="AV12" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW12" s="1" t="n">
+        <v>0.5762</v>
+      </c>
+      <c r="AX12" s="1" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="AY12" s="1" t="n">
+        <v>0.5736</v>
+      </c>
+      <c r="AZ12" s="3" t="n">
+        <v>310966</v>
+      </c>
+      <c r="BA12" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4698,6 +5082,37 @@
           <t>03/12/26</t>
         </is>
       </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="AT13" s="1" t="n">
+        <v>1.56616</v>
+      </c>
+      <c r="AU13" s="1" t="n">
+        <v>-0.00383</v>
+      </c>
+      <c r="AV13" s="2" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AW13" s="1" t="n">
+        <v>1.57001</v>
+      </c>
+      <c r="AX13" s="1" t="n">
+        <v>1.57475</v>
+      </c>
+      <c r="AY13" s="1" t="n">
+        <v>1.56216</v>
+      </c>
+      <c r="AZ13" s="3" t="n">
+        <v>440600</v>
+      </c>
+      <c r="BA13" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4824,6 +5239,37 @@
           <t>03/12/26</t>
         </is>
       </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="AT14" s="1" t="n">
+        <v>159.73</v>
+      </c>
+      <c r="AU14" s="1" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AV14" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AW14" s="1" t="n">
+        <v>159.35</v>
+      </c>
+      <c r="AX14" s="1" t="n">
+        <v>159.746</v>
+      </c>
+      <c r="AY14" s="1" t="n">
+        <v>159.009</v>
+      </c>
+      <c r="AZ14" s="3" t="n">
+        <v>585925</v>
+      </c>
+      <c r="BA14" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4950,6 +5396,37 @@
           <t>03/12/26</t>
         </is>
       </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="AT15" s="1" t="n">
+        <v>0.9034799999999999</v>
+      </c>
+      <c r="AU15" s="1" t="n">
+        <v>-0.00143</v>
+      </c>
+      <c r="AV15" s="2" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="AW15" s="1" t="n">
+        <v>0.90493</v>
+      </c>
+      <c r="AX15" s="1" t="n">
+        <v>0.9055</v>
+      </c>
+      <c r="AY15" s="1" t="n">
+        <v>0.90221</v>
+      </c>
+      <c r="AZ15" s="3" t="n">
+        <v>474139</v>
+      </c>
+      <c r="BA15" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5074,6 +5551,37 @@
       <c r="AP16" s="4" t="inlineStr">
         <is>
           <t>03/12/26</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="AT16" s="1" t="n">
+        <v>0.79133</v>
+      </c>
+      <c r="AU16" s="1" t="n">
+        <v>0.00524</v>
+      </c>
+      <c r="AV16" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AW16" s="1" t="n">
+        <v>0.78609</v>
+      </c>
+      <c r="AX16" s="1" t="n">
+        <v>0.79172</v>
+      </c>
+      <c r="AY16" s="1" t="n">
+        <v>0.78474</v>
+      </c>
+      <c r="AZ16" s="3" t="n">
+        <v>406205</v>
+      </c>
+      <c r="BA16" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
         </is>
       </c>
     </row>

--- a/outputs/march.xlsx
+++ b/outputs/march.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3535,9 +3536,7 @@
       <c r="AY3" s="1" t="n">
         <v>99.59</v>
       </c>
-      <c r="AZ3" s="3" t="n">
-        <v/>
-      </c>
+      <c r="AZ3" s="3" t="n"/>
       <c r="BA3" s="4" t="inlineStr">
         <is>
           <t>03/13/26</t>
@@ -5582,6 +5581,562 @@
       <c r="BA16" s="4" t="inlineStr">
         <is>
           <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>74039.47</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>2675.92</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>72794.36</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>74428.25</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>70419.74000000001</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>276170198</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>100.43</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>100.48</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>99.66</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>0.86373</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>0.00026</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0.8628</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>0.86253</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>562409</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0.5571</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.5528999999999999</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0.5572</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0.5516</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>922767</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>1.36863</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>1.3718</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>1.37287</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>1.36533</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>342418</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.96784</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.01029</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.95995</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.9682500000000001</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.95842</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>404042</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>80.744</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>80.56999999999999</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>81.627</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>77.19</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>184959</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>5006.47</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>-13.51</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>5019.4</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>5037.45</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>4970.32</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>180141</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>0.5756</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>0.5757</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>286516</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>1.57454</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>0.00838</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>1.56633</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>1.57612</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>1.56556</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>395952</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>159.056</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>-0.674</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>159.615</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>159.744</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>158.852</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>509185</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>0.9063099999999999</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.00283</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>0.90354</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>0.9065800000000001</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>0.90302</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>441562</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>0.78776</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>-0.00358</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>0.79071</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.79228</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>0.78651</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>357193</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
         </is>
       </c>
     </row>

--- a/outputs/march.xlsx
+++ b/outputs/march.xlsx
@@ -5595,7 +5595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:AE16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5644,6 +5644,96 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5677,6 +5767,68 @@
           <t>03/16/26</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>74516.55</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>477.08</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>74861.47</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>75905.28</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>73508.71000000001</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>214396437</v>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="n">
+        <v>71238.28999999999</v>
+      </c>
+      <c r="Y2" s="1" t="n">
+        <v>-3278.26</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="AA2" s="1" t="n">
+        <v>73910.02</v>
+      </c>
+      <c r="AB2" s="1" t="n">
+        <v>74778.42999999999</v>
+      </c>
+      <c r="AC2" s="1" t="n">
+        <v>70533.24000000001</v>
+      </c>
+      <c r="AD2" s="3" t="n">
+        <v>191810762</v>
+      </c>
+      <c r="AE2" s="4" t="inlineStr">
+        <is>
+          <t>03/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5702,10 +5854,70 @@
       <c r="G3" s="1" t="n">
         <v>99.66</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>99.56999999999999</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>100.11</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v/>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>100.19</v>
+      </c>
+      <c r="Y3" s="1" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="AB3" s="1" t="n">
+        <v>100.31</v>
+      </c>
+      <c r="AC3" s="1" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>
         </is>
@@ -5743,6 +5955,68 @@
           <t>03/16/26</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>0.86405</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>0.00032</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>0.86373</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>0.86456</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>0.86324</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>511297</v>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>0.86382</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>-0.00023</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>0.8640600000000001</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>0.86509</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>0.86283</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>564989</v>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>03/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5776,6 +6050,68 @@
           <t>03/16/26</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0.5576</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0.5571</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>0.5596</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>837740</v>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>0.5572</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>0.5576</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>0.5558999999999999</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>875842</v>
+      </c>
+      <c r="AE5" s="4" t="inlineStr">
+        <is>
+          <t>03/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5809,6 +6145,68 @@
           <t>03/16/26</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>1.36904</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>1.36863</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>1.37223</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>1.36805</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>310178</v>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>1.37319</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>0.00415</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>1.36905</v>
+      </c>
+      <c r="AB6" s="1" t="n">
+        <v>1.37375</v>
+      </c>
+      <c r="AC6" s="1" t="n">
+        <v>1.36874</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>353578</v>
+      </c>
+      <c r="AE6" s="4" t="inlineStr">
+        <is>
+          <t>03/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5842,6 +6240,68 @@
           <t>03/16/26</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.97272</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0.00488</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.96784</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.97489</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0.9648600000000001</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>363922</v>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>0.96453</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>-0.008189999999999999</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>0.97272</v>
+      </c>
+      <c r="AB7" s="1" t="n">
+        <v>0.97619</v>
+      </c>
+      <c r="AC7" s="1" t="n">
+        <v>0.96401</v>
+      </c>
+      <c r="AD7" s="3" t="n">
+        <v>390650</v>
+      </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>03/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5875,6 +6335,68 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="AB8" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="AC8" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="AD8" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="AE8" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5908,6 +6430,68 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="AB9" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="AC9" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="AD9" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5941,6 +6525,68 @@
           <t>03/16/26</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>79.285</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>-1.459</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>80.74299999999999</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>82.533</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>78.324</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>155608</v>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>75.39700000000001</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>-3.888</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>79.285</v>
+      </c>
+      <c r="AB10" s="1" t="n">
+        <v>80.167</v>
+      </c>
+      <c r="AC10" s="1" t="n">
+        <v>75.032</v>
+      </c>
+      <c r="AD10" s="3" t="n">
+        <v>174037</v>
+      </c>
+      <c r="AE10" s="4" t="inlineStr">
+        <is>
+          <t>03/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5974,6 +6620,68 @@
           <t>03/16/26</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>5005.66</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>5006.47</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>5044.26</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>4975.69</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>154893</v>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>4818.94</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>-186.72</v>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <v>5005.62</v>
+      </c>
+      <c r="AB11" s="1" t="n">
+        <v>5016.25</v>
+      </c>
+      <c r="AC11" s="1" t="n">
+        <v>4807.68</v>
+      </c>
+      <c r="AD11" s="3" t="n">
+        <v>174142</v>
+      </c>
+      <c r="AE11" s="4" t="inlineStr">
+        <is>
+          <t>03/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6007,6 +6715,68 @@
           <t>03/16/26</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0.5732</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0.5756</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.5768</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.5727</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>256808</v>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AA12" s="1" t="n">
+        <v>0.5732</v>
+      </c>
+      <c r="AB12" s="1" t="n">
+        <v>0.5778</v>
+      </c>
+      <c r="AC12" s="1" t="n">
+        <v>0.5728</v>
+      </c>
+      <c r="AD12" s="3" t="n">
+        <v>289134</v>
+      </c>
+      <c r="AE12" s="4" t="inlineStr">
+        <is>
+          <t>03/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6040,6 +6810,68 @@
           <t>03/16/26</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0.00546</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>1.57455</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>1.58175</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>1.57049</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>363725</v>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>1.57257</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <v>-0.00743</v>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB13" s="1" t="n">
+        <v>1.58274</v>
+      </c>
+      <c r="AC13" s="1" t="n">
+        <v>1.57239</v>
+      </c>
+      <c r="AD13" s="3" t="n">
+        <v>409108</v>
+      </c>
+      <c r="AE13" s="4" t="inlineStr">
+        <is>
+          <t>03/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6073,6 +6905,68 @@
           <t>03/16/26</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>158.999</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>159.057</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>159.496</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>158.723</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>446089</v>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>159.876</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="AB14" s="1" t="n">
+        <v>159.898</v>
+      </c>
+      <c r="AC14" s="1" t="n">
+        <v>158.569</v>
+      </c>
+      <c r="AD14" s="3" t="n">
+        <v>526292</v>
+      </c>
+      <c r="AE14" s="4" t="inlineStr">
+        <is>
+          <t>03/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6106,6 +7000,68 @@
           <t>03/16/26</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>0.90561</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>0.9063099999999999</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>0.90715</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>0.90491</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>373947</v>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>0.90838</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>0.00277</v>
+      </c>
+      <c r="Z15" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>0.90561</v>
+      </c>
+      <c r="AB15" s="1" t="n">
+        <v>0.91023</v>
+      </c>
+      <c r="AC15" s="1" t="n">
+        <v>0.9053099999999999</v>
+      </c>
+      <c r="AD15" s="3" t="n">
+        <v>442917</v>
+      </c>
+      <c r="AE15" s="4" t="inlineStr">
+        <is>
+          <t>03/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6137,6 +7093,68 @@
       <c r="I16" s="4" t="inlineStr">
         <is>
           <t>03/16/26</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>0.78469</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>-0.00307</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>0.78776</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>0.79003</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>0.78438</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>307988</v>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>03/17/26</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>0.79326</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>0.008569999999999999</v>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AA16" s="1" t="n">
+        <v>0.78469</v>
+      </c>
+      <c r="AB16" s="1" t="n">
+        <v>0.79361</v>
+      </c>
+      <c r="AC16" s="1" t="n">
+        <v>0.78456</v>
+      </c>
+      <c r="AD16" s="3" t="n">
+        <v>364510</v>
+      </c>
+      <c r="AE16" s="4" t="inlineStr">
+        <is>
+          <t>03/18/26</t>
         </is>
       </c>
     </row>

--- a/outputs/march.xlsx
+++ b/outputs/march.xlsx
@@ -5595,7 +5595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE16"/>
+  <dimension ref="A1:AP16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5734,6 +5734,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5829,6 +5874,37 @@
           <t>03/18/26</t>
         </is>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="AI2" s="1" t="n">
+        <v>70459.09</v>
+      </c>
+      <c r="AJ2" s="1" t="n">
+        <v>-779.2</v>
+      </c>
+      <c r="AK2" s="2" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AL2" s="1" t="n">
+        <v>71256.44</v>
+      </c>
+      <c r="AM2" s="1" t="n">
+        <v>71522.58</v>
+      </c>
+      <c r="AN2" s="1" t="n">
+        <v>68914.3</v>
+      </c>
+      <c r="AO2" s="3" t="n">
+        <v>213711036</v>
+      </c>
+      <c r="AP2" s="4" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5883,9 +5959,7 @@
       <c r="R3" s="1" t="n">
         <v>99.5</v>
       </c>
-      <c r="S3" s="3" t="n">
-        <v/>
-      </c>
+      <c r="S3" s="3" t="n"/>
       <c r="T3" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>
@@ -5914,10 +5988,39 @@
       <c r="AC3" s="1" t="n">
         <v>99.45999999999999</v>
       </c>
-      <c r="AD3" s="3" t="n">
+      <c r="AD3" s="3" t="n"/>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="AI3" s="1" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="AJ3" s="1" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="AK3" s="2" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="AL3" s="1" t="n">
+        <v>100.21</v>
+      </c>
+      <c r="AM3" s="1" t="n">
+        <v>100.31</v>
+      </c>
+      <c r="AN3" s="1" t="n">
+        <v>98.97</v>
+      </c>
+      <c r="AO3" s="3" t="n">
         <v/>
       </c>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AP3" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>
         </is>
@@ -6017,6 +6120,37 @@
           <t>03/18/26</t>
         </is>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="AI4" s="1" t="n">
+        <v>0.8628</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>-0.00102</v>
+      </c>
+      <c r="AK4" s="2" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>0.86382</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>0.86489</v>
+      </c>
+      <c r="AN4" s="1" t="n">
+        <v>0.8611799999999999</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>674587</v>
+      </c>
+      <c r="AP4" s="4" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6112,6 +6246,37 @@
           <t>03/18/26</t>
         </is>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="AI5" s="1" t="n">
+        <v>0.5586</v>
+      </c>
+      <c r="AJ5" s="1" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="AK5" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AL5" s="1" t="n">
+        <v>0.5572</v>
+      </c>
+      <c r="AM5" s="1" t="n">
+        <v>0.5613</v>
+      </c>
+      <c r="AN5" s="1" t="n">
+        <v>0.5557</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>1114302</v>
+      </c>
+      <c r="AP5" s="4" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6207,6 +6372,37 @@
           <t>03/18/26</t>
         </is>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="AI6" s="1" t="n">
+        <v>1.37391</v>
+      </c>
+      <c r="AJ6" s="1" t="n">
+        <v>0.00072</v>
+      </c>
+      <c r="AK6" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AL6" s="1" t="n">
+        <v>1.3732</v>
+      </c>
+      <c r="AM6" s="1" t="n">
+        <v>1.37481</v>
+      </c>
+      <c r="AN6" s="1" t="n">
+        <v>1.3705</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>418585</v>
+      </c>
+      <c r="AP6" s="4" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6302,6 +6498,37 @@
           <t>03/18/26</t>
         </is>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="AI7" s="1" t="n">
+        <v>0.97371</v>
+      </c>
+      <c r="AJ7" s="1" t="n">
+        <v>0.009180000000000001</v>
+      </c>
+      <c r="AK7" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AL7" s="1" t="n">
+        <v>0.96453</v>
+      </c>
+      <c r="AM7" s="1" t="n">
+        <v>0.97466</v>
+      </c>
+      <c r="AN7" s="1" t="n">
+        <v>0.96111</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>501437</v>
+      </c>
+      <c r="AP7" s="4" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6397,6 +6624,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="AI8" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="AJ8" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="AK8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AL8" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="AM8" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="AN8" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="AP8" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6492,6 +6750,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="AI9" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="AJ9" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="AK9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AL9" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="AM9" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="AN9" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="AP9" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6587,6 +6876,37 @@
           <t>03/18/26</t>
         </is>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="AI10" s="1" t="n">
+        <v>72.819</v>
+      </c>
+      <c r="AJ10" s="1" t="n">
+        <v>-2.578</v>
+      </c>
+      <c r="AK10" s="2" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="AL10" s="1" t="n">
+        <v>75.396</v>
+      </c>
+      <c r="AM10" s="1" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="AN10" s="1" t="n">
+        <v>65.637</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>220786</v>
+      </c>
+      <c r="AP10" s="4" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6682,6 +7002,37 @@
           <t>03/18/26</t>
         </is>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="AI11" s="1" t="n">
+        <v>4653.39</v>
+      </c>
+      <c r="AJ11" s="1" t="n">
+        <v>-165.55</v>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="AL11" s="1" t="n">
+        <v>4818.93</v>
+      </c>
+      <c r="AM11" s="1" t="n">
+        <v>4866.67</v>
+      </c>
+      <c r="AN11" s="1" t="n">
+        <v>4505.2</v>
+      </c>
+      <c r="AO11" s="3" t="n">
+        <v>218369</v>
+      </c>
+      <c r="AP11" s="4" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6777,6 +7128,37 @@
           <t>03/18/26</t>
         </is>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="AI12" s="1" t="n">
+        <v>0.5737</v>
+      </c>
+      <c r="AJ12" s="1" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="AL12" s="1" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="AM12" s="1" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="AN12" s="1" t="n">
+        <v>0.5729</v>
+      </c>
+      <c r="AO12" s="3" t="n">
+        <v>348869</v>
+      </c>
+      <c r="AP12" s="4" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6872,6 +7254,37 @@
           <t>03/18/26</t>
         </is>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="AI13" s="1" t="n">
+        <v>1.59203</v>
+      </c>
+      <c r="AJ13" s="1" t="n">
+        <v>0.01946</v>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL13" s="1" t="n">
+        <v>1.57258</v>
+      </c>
+      <c r="AM13" s="1" t="n">
+        <v>1.59276</v>
+      </c>
+      <c r="AN13" s="1" t="n">
+        <v>1.57186</v>
+      </c>
+      <c r="AO13" s="3" t="n">
+        <v>456264</v>
+      </c>
+      <c r="AP13" s="4" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6967,6 +7380,37 @@
           <t>03/18/26</t>
         </is>
       </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="AI14" s="1" t="n">
+        <v>157.708</v>
+      </c>
+      <c r="AJ14" s="1" t="n">
+        <v>-2.168</v>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="AL14" s="1" t="n">
+        <v>159.876</v>
+      </c>
+      <c r="AM14" s="1" t="n">
+        <v>159.876</v>
+      </c>
+      <c r="AN14" s="1" t="n">
+        <v>157.512</v>
+      </c>
+      <c r="AO14" s="3" t="n">
+        <v>651436</v>
+      </c>
+      <c r="AP14" s="4" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7062,6 +7506,37 @@
           <t>03/18/26</t>
         </is>
       </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="AI15" s="1" t="n">
+        <v>0.91337</v>
+      </c>
+      <c r="AJ15" s="1" t="n">
+        <v>0.00498</v>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AL15" s="1" t="n">
+        <v>0.90838</v>
+      </c>
+      <c r="AM15" s="1" t="n">
+        <v>0.91415</v>
+      </c>
+      <c r="AN15" s="1" t="n">
+        <v>0.9069</v>
+      </c>
+      <c r="AO15" s="3" t="n">
+        <v>581100</v>
+      </c>
+      <c r="AP15" s="4" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7155,6 +7630,37 @@
       <c r="AE16" s="4" t="inlineStr">
         <is>
           <t>03/18/26</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="AI16" s="1" t="n">
+        <v>0.78816</v>
+      </c>
+      <c r="AJ16" s="1" t="n">
+        <v>-0.00511</v>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="AL16" s="1" t="n">
+        <v>0.79326</v>
+      </c>
+      <c r="AM16" s="1" t="n">
+        <v>0.7958</v>
+      </c>
+      <c r="AN16" s="1" t="n">
+        <v>0.78578</v>
+      </c>
+      <c r="AO16" s="3" t="n">
+        <v>520290</v>
+      </c>
+      <c r="AP16" s="4" t="inlineStr">
+        <is>
+          <t>03/19/26</t>
         </is>
       </c>
     </row>

--- a/outputs/march.xlsx
+++ b/outputs/march.xlsx
@@ -5595,7 +5595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP16"/>
+  <dimension ref="A1:BA18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5779,6 +5779,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5905,6 +5950,37 @@
           <t>03/19/26</t>
         </is>
       </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="AT2" s="1" t="n">
+        <v>24101.5</v>
+      </c>
+      <c r="AU2" s="1" t="n">
+        <v>-478.5</v>
+      </c>
+      <c r="AV2" s="2" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="AW2" s="1" t="n">
+        <v>24632.75</v>
+      </c>
+      <c r="AX2" s="1" t="n">
+        <v>24660.5</v>
+      </c>
+      <c r="AY2" s="1" t="n">
+        <v>23971.25</v>
+      </c>
+      <c r="AZ2" s="3" t="n">
+        <v>584456</v>
+      </c>
+      <c r="BA2" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6017,12 +6093,41 @@
       <c r="AN3" s="1" t="n">
         <v>98.97</v>
       </c>
-      <c r="AO3" s="3" t="n">
-        <v/>
-      </c>
+      <c r="AO3" s="3" t="n"/>
       <c r="AP3" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="AT3" s="1" t="n">
+        <v>582.0599999999999</v>
+      </c>
+      <c r="AU3" s="1" t="n">
+        <v>-10.96</v>
+      </c>
+      <c r="AV3" s="2" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="AW3" s="1" t="n">
+        <v>591.0599999999999</v>
+      </c>
+      <c r="AX3" s="1" t="n">
+        <v>591.17</v>
+      </c>
+      <c r="AY3" s="1" t="n">
+        <v>578.54</v>
+      </c>
+      <c r="AZ3" s="3" t="n">
+        <v>88444945</v>
+      </c>
+      <c r="BA3" s="4" t="inlineStr">
+        <is>
+          <t>03/20/26</t>
         </is>
       </c>
     </row>
@@ -6151,6 +6256,37 @@
           <t>03/19/26</t>
         </is>
       </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="AT4" s="1" t="n">
+        <v>70047.71000000001</v>
+      </c>
+      <c r="AU4" s="1" t="n">
+        <v>-411.38</v>
+      </c>
+      <c r="AV4" s="2" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="AW4" s="1" t="n">
+        <v>69907.71000000001</v>
+      </c>
+      <c r="AX4" s="1" t="n">
+        <v>71328.19</v>
+      </c>
+      <c r="AY4" s="1" t="n">
+        <v>69500.67</v>
+      </c>
+      <c r="AZ4" s="3" t="n">
+        <v>156210978</v>
+      </c>
+      <c r="BA4" s="4" t="inlineStr">
+        <is>
+          <t>03/20/26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6277,6 +6413,37 @@
           <t>03/19/26</t>
         </is>
       </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="AT5" s="1" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="AU5" s="1" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AV5" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AW5" s="1" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="AX5" s="1" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="AY5" s="1" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="AZ5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="BA5" s="4" t="inlineStr">
+        <is>
+          <t>03/20/26</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6403,6 +6570,37 @@
           <t>03/19/26</t>
         </is>
       </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="AT6" s="1" t="n">
+        <v>0.86738</v>
+      </c>
+      <c r="AU6" s="1" t="n">
+        <v>0.00458</v>
+      </c>
+      <c r="AV6" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AW6" s="1" t="n">
+        <v>0.8628</v>
+      </c>
+      <c r="AX6" s="1" t="n">
+        <v>0.86791</v>
+      </c>
+      <c r="AY6" s="1" t="n">
+        <v>0.86149</v>
+      </c>
+      <c r="AZ6" s="3" t="n">
+        <v>607902</v>
+      </c>
+      <c r="BA6" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6529,6 +6727,37 @@
           <t>03/19/26</t>
         </is>
       </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="AT7" s="1" t="n">
+        <v>0.5535</v>
+      </c>
+      <c r="AU7" s="1" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="AV7" s="2" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="AW7" s="1" t="n">
+        <v>0.5586</v>
+      </c>
+      <c r="AX7" s="1" t="n">
+        <v>0.5601</v>
+      </c>
+      <c r="AY7" s="1" t="n">
+        <v>0.5526</v>
+      </c>
+      <c r="AZ7" s="3" t="n">
+        <v>1016232</v>
+      </c>
+      <c r="BA7" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6655,6 +6884,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="AT8" s="1" t="n">
+        <v>1.37238</v>
+      </c>
+      <c r="AU8" s="1" t="n">
+        <v>-0.00153</v>
+      </c>
+      <c r="AV8" s="2" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AW8" s="1" t="n">
+        <v>1.3739</v>
+      </c>
+      <c r="AX8" s="1" t="n">
+        <v>1.37478</v>
+      </c>
+      <c r="AY8" s="1" t="n">
+        <v>1.36997</v>
+      </c>
+      <c r="AZ8" s="3" t="n">
+        <v>403594</v>
+      </c>
+      <c r="BA8" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6781,6 +7041,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="AT9" s="1" t="n">
+        <v>0.96387</v>
+      </c>
+      <c r="AU9" s="1" t="n">
+        <v>-0.00984</v>
+      </c>
+      <c r="AV9" s="2" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="AW9" s="1" t="n">
+        <v>0.9737</v>
+      </c>
+      <c r="AX9" s="1" t="n">
+        <v>0.97444</v>
+      </c>
+      <c r="AY9" s="1" t="n">
+        <v>0.9609799999999999</v>
+      </c>
+      <c r="AZ9" s="3" t="n">
+        <v>465392</v>
+      </c>
+      <c r="BA9" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6907,6 +7198,37 @@
           <t>03/19/26</t>
         </is>
       </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="AT10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="AU10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="AV10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AW10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="AX10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="AY10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="AZ10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="BA10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7033,6 +7355,37 @@
           <t>03/19/26</t>
         </is>
       </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="AT11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="AU11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="AV11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AW11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="AX11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="AY11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="AZ11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="BA11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7159,6 +7512,37 @@
           <t>03/19/26</t>
         </is>
       </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="AT12" s="1" t="n">
+        <v>68.014</v>
+      </c>
+      <c r="AU12" s="1" t="n">
+        <v>-4.805</v>
+      </c>
+      <c r="AV12" s="2" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AW12" s="1" t="n">
+        <v>72.818</v>
+      </c>
+      <c r="AX12" s="1" t="n">
+        <v>74.535</v>
+      </c>
+      <c r="AY12" s="1" t="n">
+        <v>67.708</v>
+      </c>
+      <c r="AZ12" s="3" t="n">
+        <v>215759</v>
+      </c>
+      <c r="BA12" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7285,6 +7669,37 @@
           <t>03/19/26</t>
         </is>
       </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="AT13" s="1" t="n">
+        <v>4494.97</v>
+      </c>
+      <c r="AU13" s="1" t="n">
+        <v>-158.42</v>
+      </c>
+      <c r="AV13" s="2" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AW13" s="1" t="n">
+        <v>4653.29</v>
+      </c>
+      <c r="AX13" s="1" t="n">
+        <v>4735.31</v>
+      </c>
+      <c r="AY13" s="1" t="n">
+        <v>4479.67</v>
+      </c>
+      <c r="AZ13" s="3" t="n">
+        <v>221375</v>
+      </c>
+      <c r="BA13" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7411,6 +7826,37 @@
           <t>03/19/26</t>
         </is>
       </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="AT14" s="1" t="n">
+        <v>0.5742</v>
+      </c>
+      <c r="AU14" s="1" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="AV14" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW14" s="1" t="n">
+        <v>0.5737</v>
+      </c>
+      <c r="AX14" s="1" t="n">
+        <v>0.5758</v>
+      </c>
+      <c r="AY14" s="1" t="n">
+        <v>0.5729</v>
+      </c>
+      <c r="AZ14" s="3" t="n">
+        <v>314248</v>
+      </c>
+      <c r="BA14" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7537,6 +7983,37 @@
           <t>03/19/26</t>
         </is>
       </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="AT15" s="1" t="n">
+        <v>1.58807</v>
+      </c>
+      <c r="AU15" s="1" t="n">
+        <v>-0.00396</v>
+      </c>
+      <c r="AV15" s="2" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AW15" s="1" t="n">
+        <v>1.59203</v>
+      </c>
+      <c r="AX15" s="1" t="n">
+        <v>1.59314</v>
+      </c>
+      <c r="AY15" s="1" t="n">
+        <v>1.582</v>
+      </c>
+      <c r="AZ15" s="3" t="n">
+        <v>460655</v>
+      </c>
+      <c r="BA15" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7661,6 +8138,103 @@
       <c r="AP16" s="4" t="inlineStr">
         <is>
           <t>03/19/26</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="AT16" s="1" t="n">
+        <v>159.228</v>
+      </c>
+      <c r="AU16" s="1" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AV16" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AW16" s="1" t="n">
+        <v>157.709</v>
+      </c>
+      <c r="AX16" s="1" t="n">
+        <v>159.388</v>
+      </c>
+      <c r="AY16" s="1" t="n">
+        <v>157.628</v>
+      </c>
+      <c r="AZ16" s="3" t="n">
+        <v>565591</v>
+      </c>
+      <c r="BA16" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="AT17" s="1" t="n">
+        <v>0.91184</v>
+      </c>
+      <c r="AU17" s="1" t="n">
+        <v>-0.00153</v>
+      </c>
+      <c r="AV17" s="2" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AW17" s="1" t="n">
+        <v>0.91337</v>
+      </c>
+      <c r="AX17" s="1" t="n">
+        <v>0.9135</v>
+      </c>
+      <c r="AY17" s="1" t="n">
+        <v>0.90917</v>
+      </c>
+      <c r="AZ17" s="3" t="n">
+        <v>498580</v>
+      </c>
+      <c r="BA17" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="AT18" s="1" t="n">
+        <v>0.78799</v>
+      </c>
+      <c r="AU18" s="1" t="n">
+        <v>-0.00017</v>
+      </c>
+      <c r="AV18" s="2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AW18" s="1" t="n">
+        <v>0.78817</v>
+      </c>
+      <c r="AX18" s="1" t="n">
+        <v>0.79057</v>
+      </c>
+      <c r="AY18" s="1" t="n">
+        <v>0.78554</v>
+      </c>
+      <c r="AZ18" s="3" t="n">
+        <v>434226</v>
+      </c>
+      <c r="BA18" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
         </is>
       </c>
     </row>

--- a/outputs/march.xlsx
+++ b/outputs/march.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Week4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6436,9 +6437,7 @@
       <c r="AY5" s="1" t="n">
         <v>99.25</v>
       </c>
-      <c r="AZ5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="AZ5" s="3" t="n"/>
       <c r="BA5" s="4" t="inlineStr">
         <is>
           <t>03/20/26</t>
@@ -8235,6 +8234,628 @@
       <c r="BA18" s="4" t="inlineStr">
         <is>
           <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>24408.25</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>306.75</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>23902</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>24763</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>23772.5</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>672795</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>588</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>590.52</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>595.08</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>585.96</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>89010125</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>03/23/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>70910.33</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>862.62</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>67869.17</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>71701.37</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>67480</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>244543362</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>03/23/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>99.12</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.86481</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>-0.00257</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.86678</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.86794</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.86312</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>767862</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>03/23/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5513</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5521</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5483</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1240828</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>03/23/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.37261</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.00023</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.37194</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.37547</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.36703</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>464094</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>03/23/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.96233</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>-0.00154</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.96074</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.96689</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.95046</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>570362</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>03/23/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>69.11799999999999</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>67.956</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>70.75700000000001</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>61.036</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>240368</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>03/23/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4406.83</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>-88.14</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4494.2</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4534.96</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4100.32</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>251103</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>03/23/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5729</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5747</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5775</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>355554</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>03/23/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.59407</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.58772</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.59608</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.57927</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>504667</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>03/23/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>158.44</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>-0.788</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>159.349</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>159.655</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>158.022</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>728708</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>03/23/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.91318</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0.00134</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.9102</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.9145799999999999</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.90935</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>582020</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>03/23/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.78638</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>-0.00161</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.78971</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.79399</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.78347</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>580298</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>03/23/26</t>
         </is>
       </c>
     </row>

--- a/outputs/march.xlsx
+++ b/outputs/march.xlsx
@@ -8421,9 +8421,7 @@
       <c r="G5" s="1" t="n">
         <v>98.88</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>

--- a/outputs/march.xlsx
+++ b/outputs/march.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Week4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Week5" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8860,4 +8861,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>23139.75</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>-188.75</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>23189.5</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>23574</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>23024.5</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>549765</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>558.28</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>567.38</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>568.05</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>555.6</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>69737219</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>66665.24000000001</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>651.99</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>66051.42999999999</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>68107.86</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>65025.97</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>178520987</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>100.48</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>100.22</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.86939</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0.00151</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.86713</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.86982</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.86678</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>516636</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5479000000000001</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5493</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5465</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>875214</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.39245</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.00311</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.38665</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.3945</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.38665</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>343962</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.95421</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>-0.00103</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.95191</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.95589</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.95094</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>355943</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>70.113</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>69.705</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>71.702</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>67.742</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>200552</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4511.23</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4493.21</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4580.08</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4420.8</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>213571</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5742</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5747</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5756</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5738</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>262912</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.59601</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>-0.00302</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.59494</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.6006</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.59363</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>388590</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>159.724</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>-0.573</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>160.178</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>160.461</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>159.329</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>536331</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.9164</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>-0.00325</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.91814</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.92005</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.91608</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>395208</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.7995100000000001</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.7982</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.8012899999999999</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.79792</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>386789</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/march.xlsx
+++ b/outputs/march.xlsx
@@ -9042,9 +9042,7 @@
       <c r="G5" s="1" t="n">
         <v>100.05</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>
